--- a/Processus application.xlsx
+++ b/Processus application.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ewald\Desktop\LE LOCATAIRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7FFD13-5FB9-4099-8E86-D879FE437220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43999528-67CD-42C7-833B-76206230F1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C4DB092D-13B6-4916-9EAC-D3601856AEC5}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
   <si>
     <t>Processus application LE LOCATAIRE</t>
   </si>
@@ -141,7 +142,121 @@
   </si>
   <si>
     <t>réception dans 
-l'application</t>
+l'application du locataire</t>
+  </si>
+  <si>
+    <t>bailleurs</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>celui du locataire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">le stockages des médias faire des compressions </t>
+  </si>
+  <si>
+    <t>le stockage des désordres pour que l'IA diagnostique se rappel permet d'apprendre et fluidité la plupar des problemes dans un logements sont répétitifent</t>
+  </si>
+  <si>
+    <t>application</t>
+  </si>
+  <si>
+    <t>les interfaces web</t>
+  </si>
+  <si>
+    <t>installation de l'application</t>
+  </si>
+  <si>
+    <t>identification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nom
+prénom
+numero de logement
+étage
+bâtiment
+rue
+adresse
+</t>
+  </si>
+  <si>
+    <t>adressage</t>
+  </si>
+  <si>
+    <t>date du contrat</t>
+  </si>
+  <si>
+    <t>identité bailleur</t>
+  </si>
+  <si>
+    <t>jour
+mois
+anné</t>
+  </si>
+  <si>
+    <t>application
+LE LOCATAIRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gestion
+</t>
+  </si>
+  <si>
+    <t>autorisation</t>
+  </si>
+  <si>
+    <t>autorise</t>
+  </si>
+  <si>
+    <t>gestion</t>
+  </si>
+  <si>
+    <t>ticket bailleur</t>
+  </si>
+  <si>
+    <t>ticket locatif</t>
+  </si>
+  <si>
+    <t>ticket annulé</t>
+  </si>
+  <si>
+    <t>locatif</t>
+  </si>
+  <si>
+    <t>rejeter</t>
+  </si>
+  <si>
+    <t>réclamations
+ technique</t>
+  </si>
+  <si>
+    <t>charge bailleur</t>
+  </si>
+  <si>
+    <t>diagnostic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">si prestataire pour travaux </t>
+  </si>
+  <si>
+    <t>si pas de prestataire pour travaux</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>autorisation X</t>
+  </si>
+  <si>
+    <t>l'agence  du secteur 1</t>
+  </si>
+  <si>
+    <t>autorisation secteur2</t>
+  </si>
+  <si>
+    <t>gestion des prestataires pour travaux locatif</t>
   </si>
 </sst>
 </file>
@@ -165,7 +280,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -225,23 +340,281 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -249,6 +622,23 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -258,11 +648,99 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -287,13 +765,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>228896</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>184593</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>443023</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -340,13 +818,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>59069</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>59069</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>132907</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -393,13 +871,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>657152</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>59070</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>310117</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>95989</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -446,13 +924,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>502093</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>118140</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>59069</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -499,13 +977,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>413489</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>66454</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>450407</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>73837</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -552,13 +1030,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>322226</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>78563</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>649767</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>81220</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -605,13 +1083,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>228896</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>66454</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>1107558</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>66454</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -658,13 +1136,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>258430</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>73837</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>1107558</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>88605</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -699,6 +1177,1160 @@
         </a:fillRef>
         <a:effectRef idx="0">
           <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>754673</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>21981</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>136542</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>58900</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Connecteur droit avec flèche 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC0447EA-D1BD-4864-87D9-4F728FCC68EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="754673" y="974481"/>
+          <a:ext cx="7258311" cy="36919"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>73269</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>43961</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Connecteur droit avec flèche 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAF6C974-52CA-41F9-B316-CAFCE856E851}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1692519" y="4286250"/>
+          <a:ext cx="1509346" cy="7327"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>21981</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>115766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>117231</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="Connecteur droit avec flèche 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4B2AD92-3875-48A6-BD20-60A3D54BFBDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6139962" y="4314093"/>
+          <a:ext cx="1742342" cy="1465"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>282086</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>14653</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>282088</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Connecteur droit avec flèche 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E0F7678-13C9-4366-B23C-FE8FF9D54C2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1619250" y="5645394"/>
+          <a:ext cx="337038" cy="2"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>13189</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>225669</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>13188</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>225671</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Connecteur droit avec flèche 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27BA9FC7-2583-4726-A2FB-06E3AB87D40C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2834054" y="5772150"/>
+          <a:ext cx="337038" cy="2"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>744416</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>252778</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>249115</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>252778</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Connecteur droit avec flèche 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEF80FAC-DB86-46F5-B825-6AA025909239}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3902320" y="5616086"/>
+          <a:ext cx="266699" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>41031</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>124558</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>378069</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>124560</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Connecteur droit avec flèche 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF446459-B651-4E38-A1B0-D2AD119120D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="11434396" y="6418385"/>
+          <a:ext cx="337038" cy="2"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>32239</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>240323</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>54220</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>240325</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="Connecteur droit avec flèche 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F852BBFB-42BD-4947-A9D3-B97840403C0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6150220" y="5786804"/>
+          <a:ext cx="337038" cy="2"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>322385</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>337038</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>102577</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>161192</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="Connecteur droit avec flèche 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2601005D-B5AF-4497-862A-F13BD12AC37B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9437077" y="6279173"/>
+          <a:ext cx="644769" cy="175846"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>32238</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>93785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>369276</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>93787</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="Connecteur droit avec flèche 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6222832-5E9F-4DCC-969A-0E4045B9B5E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="11425603" y="6783266"/>
+          <a:ext cx="337038" cy="2"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>150935</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>375138</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>150937</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="Connecteur droit avec flèche 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91AFD5FF-A4B5-448E-8A8F-2D9D5717177D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="11431465" y="7236070"/>
+          <a:ext cx="337038" cy="2"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>307731</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>29308</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>13188</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>145073</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="54" name="Connecteur droit avec flèche 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA340DD4-913E-4FAF-9314-6D3160392CD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9422423" y="6323135"/>
+          <a:ext cx="570034" cy="511419"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>278423</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>29308</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>33704</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="55" name="Connecteur droit avec flèche 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{587A8633-CD63-40C9-A5F7-C72A5622B3FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9393115" y="6323135"/>
+          <a:ext cx="619858" cy="876299"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>161192</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="Connecteur droit avec flèche 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FD3C5CD-3655-412A-A699-8AF3B6FA2B8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12734192" y="6843346"/>
+          <a:ext cx="1436078" cy="153866"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>49823</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>86456</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>725365</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="60" name="Connecteur droit avec flèche 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{488E0E68-B984-4B53-BDA2-73C85547F3BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16667285" y="6578110"/>
+          <a:ext cx="675542" cy="8794"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>73269</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>146538</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="Connecteur droit avec flèche 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB2B2503-A107-427F-844D-BBA3B4ACD869}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="12646269" y="6638192"/>
+          <a:ext cx="1524000" cy="139212"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>121626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>694592</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>130420</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="68" name="Connecteur droit avec flèche 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{939A61D5-476C-4E8D-B458-A09DA98D6856}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18922512" y="6613280"/>
+          <a:ext cx="675542" cy="8794"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>79131</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>424961</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>293077</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>71804</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="69" name="Connecteur droit avec flèche 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAB17474-2242-4ADE-9E34-8FD719883973}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="12652131" y="5788269"/>
+          <a:ext cx="1620715" cy="577362"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>527539</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>73269</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>534866</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>175847</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="72" name="Connecteur droit 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AA5FD2E-20DF-481B-B882-CC37C65BC677}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="4703885" y="4857750"/>
+          <a:ext cx="7327" cy="293078"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>527539</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>249116</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="74" name="Connecteur droit 73">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0403181F-8ADF-450E-B785-F2268A8E95F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4703885" y="4872404"/>
+          <a:ext cx="11503269" cy="21981"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>307732</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>117231</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>315057</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>117231</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="78" name="Connecteur droit 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE785EC9-AD9C-48FC-AC99-2B2F78086978}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="14639194" y="4901712"/>
+          <a:ext cx="7325" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>225671</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>93785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>232996</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>93785</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="80" name="Connecteur droit 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68136B13-5D55-4FA1-A145-689FF81EC187}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="16183709" y="4878266"/>
+          <a:ext cx="7325" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="tx1"/>
@@ -1007,269 +2639,1089 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CE112DA-9725-47E8-9E13-3CC5AC6B7C9E}">
-  <dimension ref="B2:X29"/>
+  <dimension ref="B2:AE80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="2"/>
-    <col min="2" max="2" width="12.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="2"/>
-    <col min="7" max="7" width="3.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="2"/>
-    <col min="9" max="9" width="4.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="2"/>
-    <col min="11" max="11" width="4.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="14" style="2" customWidth="1"/>
-    <col min="15" max="15" width="4.5703125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13" style="2" customWidth="1"/>
-    <col min="17" max="17" width="5.5703125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="5.85546875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" style="2"/>
-    <col min="21" max="21" width="6.42578125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="5.28515625" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="11.42578125" style="1"/>
+    <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="3.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="1"/>
+    <col min="11" max="11" width="4.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14" style="1" customWidth="1"/>
+    <col min="15" max="15" width="4.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.85546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.85546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="6.42578125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="5.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="13" style="1" customWidth="1"/>
+    <col min="25" max="28" width="11.42578125" style="1"/>
+    <col min="29" max="29" width="11.42578125" style="1" customWidth="1"/>
+    <col min="30" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-    </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="H7" s="13" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+    </row>
+    <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+    </row>
+    <row r="9" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="8"/>
+      <c r="D9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="37"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="36"/>
+      <c r="L9" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+    </row>
+    <row r="10" spans="2:16" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="30"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="34"/>
+      <c r="L10" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B11" s="24"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B12" s="24"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+    </row>
+    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="24"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B14" s="38"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="39"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" s="39"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B15" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+    </row>
+    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="44"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="45"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="M16" s="45"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="B17" s="5"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="B18" s="5"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="B19" s="5"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="I20" s="8"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="I21" s="8"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="X21" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="5"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="8"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" spans="2:31" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="42"/>
+      <c r="D23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="42"/>
+      <c r="F23" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" s="8"/>
+      <c r="H23" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="M23" s="42"/>
+      <c r="N23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="X23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="2:31" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I24" s="8"/>
+      <c r="K24" s="42"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I25" s="8"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8">
+        <v>1</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="5"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="W26" s="1">
+        <v>1</v>
+      </c>
+      <c r="X26" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y26" s="50"/>
+      <c r="Z26" s="51"/>
+      <c r="AB26" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC26" s="36"/>
+      <c r="AE26" s="52" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q27" s="8">
+        <v>2</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE27" s="53"/>
+    </row>
+    <row r="28" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q28" s="8"/>
+      <c r="W28" s="1">
+        <v>0</v>
+      </c>
+      <c r="X28" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="51"/>
+      <c r="AE28" s="53"/>
+    </row>
+    <row r="29" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q29" s="8">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE29" s="54"/>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="I36" s="10"/>
+      <c r="J36" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="K36" s="10"/>
+      <c r="L36" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="M36" s="10"/>
+      <c r="N36" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="O36" s="10"/>
+      <c r="P36" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="T7" s="13" t="s">
+      <c r="S36" s="10"/>
+      <c r="T36" s="21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H9" s="4" t="s">
+      <c r="U36" s="10"/>
+      <c r="V36" s="10"/>
+      <c r="W36" s="10"/>
+      <c r="X36" s="10"/>
+      <c r="Y36" s="11"/>
+    </row>
+    <row r="37" spans="2:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="12"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+      <c r="U37" s="6"/>
+      <c r="V37" s="6"/>
+      <c r="W37" s="6"/>
+      <c r="X37" s="6"/>
+      <c r="Y37" s="13"/>
+    </row>
+    <row r="38" spans="2:25" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="12"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="4" t="s">
+      <c r="I38" s="5"/>
+      <c r="J38" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="4" t="s">
+      <c r="K38" s="5"/>
+      <c r="L38" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="M38" s="6"/>
+      <c r="N38" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="O38" s="6"/>
+      <c r="P38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="R9" s="4" t="s">
+      <c r="Q38" s="6"/>
+      <c r="R38" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="T9" s="4" t="s">
+      <c r="S38" s="6"/>
+      <c r="T38" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+      <c r="U38" s="6"/>
+      <c r="V38" s="6"/>
+      <c r="W38" s="6"/>
+      <c r="X38" s="6"/>
+      <c r="Y38" s="13"/>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B39" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="C39" s="6"/>
+      <c r="D39" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="E39" s="6"/>
+      <c r="F39" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="N10" s="8"/>
-      <c r="P10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="T10" s="7"/>
-    </row>
-    <row r="11" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="N11" s="8"/>
-      <c r="P11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="T11" s="7"/>
-    </row>
-    <row r="12" spans="2:24" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
+      <c r="G39" s="6"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="6"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="6"/>
+      <c r="V39" s="6"/>
+      <c r="W39" s="6"/>
+      <c r="X39" s="6"/>
+      <c r="Y39" s="13"/>
+    </row>
+    <row r="40" spans="2:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="12"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="6"/>
+      <c r="V40" s="6"/>
+      <c r="W40" s="6"/>
+      <c r="X40" s="6"/>
+      <c r="Y40" s="13"/>
+    </row>
+    <row r="41" spans="2:25" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="C41" s="6"/>
+      <c r="D41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="E41" s="6"/>
+      <c r="F41" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="H13" s="13" t="s">
+      <c r="G41" s="7"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6"/>
+      <c r="R41" s="6"/>
+      <c r="S41" s="6"/>
+      <c r="T41" s="6"/>
+      <c r="U41" s="6"/>
+      <c r="V41" s="6"/>
+      <c r="W41" s="6"/>
+      <c r="X41" s="6"/>
+      <c r="Y41" s="13"/>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B42" s="12"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="13" t="s">
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="M42" s="6"/>
+      <c r="N42" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="P13" s="13" t="s">
+      <c r="O42" s="6"/>
+      <c r="P42" s="22" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="2:24" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H15" s="4" t="s">
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6"/>
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="13"/>
+    </row>
+    <row r="43" spans="2:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="12"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
+      <c r="Q43" s="6"/>
+      <c r="R43" s="6"/>
+      <c r="S43" s="6"/>
+      <c r="T43" s="6"/>
+      <c r="U43" s="6"/>
+      <c r="V43" s="6"/>
+      <c r="W43" s="6"/>
+      <c r="X43" s="6"/>
+      <c r="Y43" s="13"/>
+    </row>
+    <row r="44" spans="2:25" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="12"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="L15" s="4" t="s">
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="M44" s="6"/>
+      <c r="N44" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="O44" s="6"/>
+      <c r="P44" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R15" s="4" t="s">
+      <c r="Q44" s="6"/>
+      <c r="R44" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T15" s="4" t="s">
+      <c r="S44" s="6"/>
+      <c r="T44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V15" s="4" t="s">
+      <c r="U44" s="6"/>
+      <c r="V44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X15" s="4" t="s">
+      <c r="W44" s="6"/>
+      <c r="X44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="F17" s="1" t="s">
+      <c r="Y44" s="13"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="14"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15"/>
+      <c r="P45" s="15"/>
+      <c r="Q45" s="15"/>
+      <c r="R45" s="15"/>
+      <c r="S45" s="15"/>
+      <c r="T45" s="15"/>
+      <c r="U45" s="15"/>
+      <c r="V45" s="15"/>
+      <c r="W45" s="15"/>
+      <c r="X45" s="15"/>
+      <c r="Y45" s="16"/>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="F46" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="L17" s="2" t="s">
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="L46" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="2:20" ht="84" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
+    <row r="47" spans="2:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="2:25" ht="84" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F48" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="L19" s="4" t="s">
+      <c r="G48" s="19"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="L48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N19" s="3" t="s">
+      <c r="N48" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P19" s="4" t="s">
+      <c r="P48" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="R19" s="4" t="s">
+      <c r="R48" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="T19" s="4" t="s">
+      <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="2:20" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
+    <row r="52" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="2:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F53" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H53" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="4" t="s">
+      <c r="L53" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="2:20" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="3" t="s">
+    <row r="57" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="2:12" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D58" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H58" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L29" s="4" t="s">
+      <c r="L58" s="3" t="s">
         <v>27</v>
       </c>
     </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B63" s="9"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="11"/>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B64" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="13"/>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65" s="12"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="13"/>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B66" s="12"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="13"/>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="12"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="13"/>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="12"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="13"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="12"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="13"/>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B70" s="14"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="16"/>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B71" s="12"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="13"/>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B72" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="13"/>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B73" s="12"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="13"/>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B74" s="14"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="16"/>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B78" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B80" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="9">
+    <mergeCell ref="AB26:AC26"/>
+    <mergeCell ref="AE26:AE29"/>
     <mergeCell ref="B2:P2"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="D7:K7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Processus application.xlsx
+++ b/Processus application.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ewald\Desktop\LE LOCATAIRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43999528-67CD-42C7-833B-76206230F1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB7F578-4FE8-4088-80F1-113DB0605314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C4DB092D-13B6-4916-9EAC-D3601856AEC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{C4DB092D-13B6-4916-9EAC-D3601856AEC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="121">
   <si>
     <t>Processus application LE LOCATAIRE</t>
   </si>
@@ -258,15 +258,221 @@
   <si>
     <t>gestion des prestataires pour travaux locatif</t>
   </si>
+  <si>
+    <t>une réclamation</t>
+  </si>
+  <si>
+    <t>fuite sous évier</t>
+  </si>
+  <si>
+    <t>questiion 1</t>
+  </si>
+  <si>
+    <t>depuis quand avez-vous constater la fuite</t>
+  </si>
+  <si>
+    <t>réponse probales</t>
+  </si>
+  <si>
+    <t>question 2</t>
+  </si>
+  <si>
+    <t>réponse probable</t>
+  </si>
+  <si>
+    <t>question 3</t>
+  </si>
+  <si>
+    <t>(quoi?)</t>
+  </si>
+  <si>
+    <t>(quand?)</t>
+  </si>
+  <si>
+    <t>avez-vous fait quelque chose nettoyer le siphond, mis du produit pour déboucher?</t>
+  </si>
+  <si>
+    <t>oui j'en ais mis hier</t>
+  </si>
+  <si>
+    <t>l'eau de votre lavabo s'écoule normalement?</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>réponse probale</t>
+  </si>
+  <si>
+    <t>oui elle s'écoule normalement</t>
+  </si>
+  <si>
+    <t>pré-diagnostic</t>
+  </si>
+  <si>
+    <t>depuis mon entrée dans le logement</t>
+  </si>
+  <si>
+    <t>oui</t>
+  </si>
+  <si>
+    <t>non</t>
+  </si>
+  <si>
+    <t>nettoyer le siphon, metter des produits vendu dans le marché et revenez ver nous</t>
+  </si>
+  <si>
+    <t>depuis mon entrée dans le logement (si dans les 4 mois et moins de 6 mois)</t>
+  </si>
+  <si>
+    <t>locataire entrant passage de l'entrepris qui à fait la REL ou d'un plombier</t>
+  </si>
+  <si>
+    <t>1 er cas</t>
+  </si>
+  <si>
+    <t>2 eme cas</t>
+  </si>
+  <si>
+    <t>fuite de toiture</t>
+  </si>
+  <si>
+    <t>penser à vous protéger vos effet personnels</t>
+  </si>
+  <si>
+    <t>oui, daccord</t>
+  </si>
+  <si>
+    <t>3eme cas</t>
+  </si>
+  <si>
+    <t>pas d'électricité dans la chambre</t>
+  </si>
+  <si>
+    <t>depuis quand</t>
+  </si>
+  <si>
+    <t>avez-vous tous débranchés et relevé le disjoncteur</t>
+  </si>
+  <si>
+    <t>le disjonteur ne reste pas</t>
+  </si>
+  <si>
+    <t>faite le, débrancher tous et faite monter le disjoncteur</t>
+  </si>
+  <si>
+    <t>il reste enclanché</t>
+  </si>
+  <si>
+    <t>probablement un appareil defectueux</t>
+  </si>
+  <si>
+    <t>oui, mais dès que jutilise un appareil le compteur saute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">êtes vous à jour de votre abonnement, avez-vous eu un retard de payement </t>
+  </si>
+  <si>
+    <t>oui à jour et pas de retard ce mois ci</t>
+  </si>
+  <si>
+    <t>oui à jour je viens de payer ma facture j'étais en retard</t>
+  </si>
+  <si>
+    <t>cela doit être un problème électrique</t>
+  </si>
+  <si>
+    <t>avez-vous appeler votre fournissuer d'électricité</t>
+  </si>
+  <si>
+    <t>quand il pleut</t>
+  </si>
+  <si>
+    <t>Comptes de test (démo)</t>
+  </si>
+  <si>
+    <t>Profil</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Mot de passe</t>
+  </si>
+  <si>
+    <t>Page après login</t>
+  </si>
+  <si>
+    <t>Référent V1</t>
+  </si>
+  <si>
+    <t>demo.referent@lelocataire.test</t>
+  </si>
+  <si>
+    <t>DemoReferent1!</t>
+  </si>
+  <si>
+    <t>/agent/reclamations</t>
+  </si>
+  <si>
+    <t>demo.bailleur@lelocataire.test</t>
+  </si>
+  <si>
+    <t>DemoBailleur1!</t>
+  </si>
+  <si>
+    <t>/bailleur/dashboard</t>
+  </si>
+  <si>
+    <t>Locataire</t>
+  </si>
+  <si>
+    <t>demo.locataire@lelocataire.test</t>
+  </si>
+  <si>
+    <t>DemoLocataire1!</t>
+  </si>
+  <si>
+    <t>App mobile</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -280,7 +486,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -604,11 +810,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -636,18 +993,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -661,24 +1006,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -686,15 +1013,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -733,6 +1051,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -742,8 +1066,97 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2672,23 +3085,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="8"/>
@@ -2758,20 +3171,20 @@
       <c r="P6" s="8"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="8"/>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="28"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
@@ -2797,17 +3210,17 @@
     </row>
     <row r="9" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C9" s="8"/>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="36"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="40"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="36"/>
-      <c r="L9" s="32" t="s">
+      <c r="I9" s="40"/>
+      <c r="L9" s="22" t="s">
         <v>40</v>
       </c>
       <c r="M9" s="8"/>
@@ -2820,17 +3233,17 @@
         <v>35</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="31"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="50"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="33" t="s">
+      <c r="H10" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="I10" s="34"/>
-      <c r="L10" s="32" t="s">
+      <c r="I10" s="24"/>
+      <c r="L10" s="22" t="s">
         <v>12</v>
       </c>
       <c r="M10" s="8"/>
@@ -2839,7 +3252,7 @@
       <c r="P10" s="8"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="24"/>
+      <c r="B11" s="20"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -2856,7 +3269,7 @@
       <c r="P11" s="8"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="24"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -2873,7 +3286,7 @@
       <c r="P12" s="8"/>
     </row>
     <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="24"/>
+      <c r="B13" s="20"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -2890,140 +3303,140 @@
       <c r="P13" s="8"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="38"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39" t="s">
+      <c r="B14" s="25"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="40"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39" t="s">
+      <c r="J14" s="33"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="39"/>
-      <c r="N14" s="40"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="27"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="43" t="s">
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="30" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="47" t="s">
+      <c r="J15" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="43" t="s">
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="30" t="s">
         <v>11</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
     </row>
     <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="44"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45" t="s">
+      <c r="B16" s="31"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="34"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="24"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45" t="s">
+      <c r="J16" s="35"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="M16" s="45"/>
-      <c r="N16" s="34"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="24"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
     </row>
     <row r="17" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
     </row>
     <row r="18" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.25">
       <c r="I20" s="8"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
     </row>
     <row r="21" spans="2:31" x14ac:dyDescent="0.25">
       <c r="I21" s="8"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="X21" s="1" t="s">
@@ -3032,22 +3445,22 @@
     </row>
     <row r="22" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42" t="s">
+      <c r="C22" s="29"/>
+      <c r="D22" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8" t="s">
         <v>12</v>
       </c>
       <c r="I22" s="8"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
       <c r="O22" s="8"/>
       <c r="P22" s="8"/>
     </row>
@@ -3055,27 +3468,27 @@
       <c r="B23" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="42"/>
+      <c r="C23" s="29"/>
       <c r="D23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="42"/>
-      <c r="F23" s="32" t="s">
+      <c r="E23" s="29"/>
+      <c r="F23" s="22" t="s">
         <v>44</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="32" t="s">
+      <c r="H23" s="22" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="8"/>
-      <c r="J23" s="32" t="s">
+      <c r="J23" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="K23" s="42"/>
-      <c r="L23" s="32" t="s">
+      <c r="K23" s="29"/>
+      <c r="L23" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M23" s="42"/>
+      <c r="M23" s="29"/>
       <c r="N23" s="3" t="s">
         <v>52</v>
       </c>
@@ -3090,9 +3503,9 @@
     </row>
     <row r="24" spans="2:31" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I24" s="8"/>
-      <c r="K24" s="42"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="42"/>
+      <c r="K24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
       <c r="O24" s="8"/>
       <c r="P24" s="1" t="s">
         <v>54</v>
@@ -3100,10 +3513,10 @@
     </row>
     <row r="25" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I25" s="8"/>
-      <c r="J25" s="42"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="42"/>
-      <c r="M25" s="42"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
       <c r="O25" s="8"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8">
@@ -3118,34 +3531,34 @@
     </row>
     <row r="26" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="5"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
       <c r="W26" s="1">
         <v>1</v>
       </c>
-      <c r="X26" s="49" t="s">
+      <c r="X26" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="Y26" s="50"/>
-      <c r="Z26" s="51"/>
-      <c r="AB26" s="35" t="s">
+      <c r="Y26" s="37"/>
+      <c r="Z26" s="38"/>
+      <c r="AB26" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="AC26" s="36"/>
-      <c r="AE26" s="52" t="s">
+      <c r="AC26" s="40"/>
+      <c r="AE26" s="41" t="s">
         <v>61</v>
       </c>
     </row>
@@ -3159,19 +3572,19 @@
       <c r="T27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AE27" s="53"/>
+      <c r="AE27" s="42"/>
     </row>
     <row r="28" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q28" s="8"/>
       <c r="W28" s="1">
         <v>0</v>
       </c>
-      <c r="X28" s="49" t="s">
+      <c r="X28" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="51"/>
-      <c r="AE28" s="53"/>
+      <c r="Y28" s="37"/>
+      <c r="Z28" s="38"/>
+      <c r="AE28" s="42"/>
     </row>
     <row r="29" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q29" s="8">
@@ -3183,7 +3596,7 @@
       <c r="T29" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AE29" s="54"/>
+      <c r="AE29" s="43"/>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B36" s="9"/>
@@ -3192,11 +3605,11 @@
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="17" t="s">
         <v>21</v>
       </c>
       <c r="I36" s="10"/>
-      <c r="J36" s="21" t="s">
+      <c r="J36" s="17" t="s">
         <v>21</v>
       </c>
       <c r="K36" s="10"/>
@@ -3204,7 +3617,7 @@
         <v>11</v>
       </c>
       <c r="M36" s="10"/>
-      <c r="N36" s="21" t="s">
+      <c r="N36" s="17" t="s">
         <v>21</v>
       </c>
       <c r="O36" s="10"/>
@@ -3216,7 +3629,7 @@
         <v>12</v>
       </c>
       <c r="S36" s="10"/>
-      <c r="T36" s="21" t="s">
+      <c r="T36" s="17" t="s">
         <v>21</v>
       </c>
       <c r="U36" s="10"/>
@@ -3300,7 +3713,7 @@
         <v>11</v>
       </c>
       <c r="E39" s="6"/>
-      <c r="F39" s="22" t="s">
+      <c r="F39" s="18" t="s">
         <v>21</v>
       </c>
       <c r="G39" s="6"/>
@@ -3350,7 +3763,7 @@
       <c r="Y40" s="13"/>
     </row>
     <row r="41" spans="2:25" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="19" t="s">
         <v>1</v>
       </c>
       <c r="C41" s="6"/>
@@ -3388,13 +3801,13 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
-      <c r="H42" s="22" t="s">
+      <c r="H42" s="18" t="s">
         <v>21</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
       <c r="K42" s="5"/>
-      <c r="L42" s="22" t="s">
+      <c r="L42" s="18" t="s">
         <v>21</v>
       </c>
       <c r="M42" s="6"/>
@@ -3402,7 +3815,7 @@
         <v>11</v>
       </c>
       <c r="O42" s="6"/>
-      <c r="P42" s="22" t="s">
+      <c r="P42" s="18" t="s">
         <v>21</v>
       </c>
       <c r="Q42" s="6"/>
@@ -3510,11 +3923,11 @@
       <c r="Y45" s="16"/>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="F46" s="17" t="s">
+      <c r="F46" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
       <c r="L46" s="1" t="s">
         <v>21</v>
       </c>
@@ -3527,11 +3940,11 @@
       <c r="D48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F48" s="18" t="s">
+      <c r="F48" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G48" s="19"/>
-      <c r="H48" s="20"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="47"/>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
       <c r="L48" s="3" t="s">
@@ -3727,4 +4140,462 @@
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F8B93DC-E733-41E3-A5BD-BBBCB27C9391}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B7:M39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="36.85546875" customWidth="1"/>
+    <col min="5" max="5" width="36" style="55" customWidth="1"/>
+    <col min="6" max="6" width="43" style="55" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" style="55" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" style="55" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" style="55" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" s="55"/>
+    </row>
+    <row r="8" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="55" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="B9" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="60"/>
+      <c r="E9" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="62"/>
+    </row>
+    <row r="10" spans="2:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="B10" s="63"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="58"/>
+      <c r="L10" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="64"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="63"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="64"/>
+    </row>
+    <row r="12" spans="2:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="B12" s="63"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="58"/>
+      <c r="L12" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="M12" s="64"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="63"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="64"/>
+    </row>
+    <row r="14" spans="2:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="B14" s="63"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="58"/>
+      <c r="L14" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="64"/>
+    </row>
+    <row r="15" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="65"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="68"/>
+    </row>
+    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:13" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="69" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="71" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="71" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="71"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="M19" s="72"/>
+    </row>
+    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="B23" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="60"/>
+      <c r="E23" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" s="61"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="73"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B24" s="63"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="64"/>
+    </row>
+    <row r="25" spans="2:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="B25" s="63"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="K25" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="L25" s="57"/>
+      <c r="M25" s="64"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B26" s="63"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="64"/>
+    </row>
+    <row r="27" spans="2:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="B27" s="63"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="J27" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="K27" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="L27" s="57"/>
+      <c r="M27" s="64"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B28" s="63"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="64"/>
+    </row>
+    <row r="29" spans="2:13" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="65"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="K29" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="L29" s="66"/>
+      <c r="M29" s="68"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J30" s="55"/>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J31" s="55"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J32" s="55"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J33" s="55"/>
+    </row>
+    <row r="34" spans="2:10" ht="81" x14ac:dyDescent="0.3">
+      <c r="B34" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
+      <c r="J34" s="55"/>
+    </row>
+    <row r="35" spans="2:10" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B35" s="76"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="J35" s="55"/>
+    </row>
+    <row r="36" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B36" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="77" t="s">
+        <v>108</v>
+      </c>
+      <c r="F36" s="77" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="B37" s="78" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="E37" s="79" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" s="79" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="B38" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="F38" s="79" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="B39" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="79" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="80" t="s">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C37" r:id="rId1" xr:uid="{6ABF34E7-3C7F-424D-88B4-503ED3F4D7BE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="43" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>